--- a/apps/web/public/assets/templates/parent-import-template.xlsx
+++ b/apps/web/public/assets/templates/parent-import-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,36 +431,65 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>必填</v>
+      </c>
+      <c r="B2" t="str">
+        <v>必填（與Email二擇一）</v>
+      </c>
+      <c r="C2" t="str">
+        <v>必填（與電話二擇一）</v>
+      </c>
+      <c r="D2" t="str">
+        <v>選填</v>
+      </c>
+      <c r="E2" t="str">
+        <v>必填</v>
+      </c>
+      <c r="F2" t="str">
+        <v>必填（見說明頁）</v>
+      </c>
+      <c r="G2" t="str">
+        <v>必填</v>
+      </c>
+      <c r="H2" t="str">
+        <v>選填（YYYY-MM-DD）</v>
+      </c>
+      <c r="I2" t="str">
+        <v>選填（見說明頁）</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>王美華</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>0912345678</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
+        <v>wang@example.com</v>
+      </c>
+      <c r="D3" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
+      <c r="E3" t="str">
         <v>王小明</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F3" t="str">
         <v>國一</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G3" t="str">
         <v>台北市立中正國中</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H3" t="str">
         <v>2012-03-15</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I3" t="str">
         <v>男</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/apps/web/public/assets/templates/parent-import-template.xlsx
+++ b/apps/web/public/assets/templates/parent-import-template.xlsx
@@ -399,6 +399,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I3"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/apps/web/public/assets/templates/parent-import-template.xlsx
+++ b/apps/web/public/assets/templates/parent-import-template.xlsx
@@ -1,59 +1,231 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="資料" sheetId="1" r:id="rId1"/>
-    <sheet name="說明" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="資料" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="說明" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+  <si>
+    <t>家長姓名 *</t>
+  </si>
+  <si>
+    <t>家長電話</t>
+  </si>
+  <si>
+    <t>家長 Email</t>
+  </si>
+  <si>
+    <t>家長備註</t>
+  </si>
+  <si>
+    <t>學生姓名 *</t>
+  </si>
+  <si>
+    <t>學生年級 *</t>
+  </si>
+  <si>
+    <t>學生就讀學校 *</t>
+  </si>
+  <si>
+    <t>學生生日</t>
+  </si>
+  <si>
+    <t>學生性別</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>必填（與 Email 二擇一）</t>
+  </si>
+  <si>
+    <t>必填（與電話二擇一）</t>
+  </si>
+  <si>
+    <t>選填</t>
+  </si>
+  <si>
+    <t>必填（見說明頁）</t>
+  </si>
+  <si>
+    <t>選填（YYYY-MM-DD）</t>
+  </si>
+  <si>
+    <t>選填（見說明頁）</t>
+  </si>
+  <si>
+    <t>王美華</t>
+  </si>
+  <si>
+    <t>0912345678</t>
+  </si>
+  <si>
+    <t>wang@example.com</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>王小明</t>
+  </si>
+  <si>
+    <t>國一</t>
+  </si>
+  <si>
+    <t>台北市立中正國中</t>
+  </si>
+  <si>
+    <t>2012-03-15</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>合法填寫值參考</t>
+  </si>
+  <si>
+    <t>年級</t>
+  </si>
+  <si>
+    <t>性別</t>
+  </si>
+  <si>
+    <t>小一</t>
+  </si>
+  <si>
+    <t>小二</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>小三</t>
+  </si>
+  <si>
+    <t>不提供</t>
+  </si>
+  <si>
+    <t>小四</t>
+  </si>
+  <si>
+    <t>小五</t>
+  </si>
+  <si>
+    <t>小六</t>
+  </si>
+  <si>
+    <t>國二</t>
+  </si>
+  <si>
+    <t>國三</t>
+  </si>
+  <si>
+    <t>高一</t>
+  </si>
+  <si>
+    <t>高二</t>
+  </si>
+  <si>
+    <t>高三</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFCC3300"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFCC7700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="FF444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E3A5F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5B9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -61,18 +233,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1E3A5F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1E3A5F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1E3A5F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1E3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFEEEEEE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,210 +645,225 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>家長姓名*</v>
-      </c>
-      <c r="B1" t="str">
-        <v>家長電話</v>
-      </c>
-      <c r="C1" t="str">
-        <v>家長Email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>家長備註</v>
-      </c>
-      <c r="E1" t="str">
-        <v>學生姓名*</v>
-      </c>
-      <c r="F1" t="str">
-        <v>學生年級*</v>
-      </c>
-      <c r="G1" t="str">
-        <v>學生就讀學校*</v>
-      </c>
-      <c r="H1" t="str">
-        <v>學生生日</v>
-      </c>
-      <c r="I1" t="str">
-        <v>學生性別</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>必填</v>
-      </c>
-      <c r="B2" t="str">
-        <v>必填（與Email二擇一）</v>
-      </c>
-      <c r="C2" t="str">
-        <v>必填（與電話二擇一）</v>
-      </c>
-      <c r="D2" t="str">
-        <v>選填</v>
-      </c>
-      <c r="E2" t="str">
-        <v>必填</v>
-      </c>
-      <c r="F2" t="str">
-        <v>必填（見說明頁）</v>
-      </c>
-      <c r="G2" t="str">
-        <v>必填</v>
-      </c>
-      <c r="H2" t="str">
-        <v>選填（YYYY-MM-DD）</v>
-      </c>
-      <c r="I2" t="str">
-        <v>選填（見說明頁）</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>王美華</v>
-      </c>
-      <c r="B3" t="str">
-        <v>0912345678</v>
-      </c>
-      <c r="C3" t="str">
-        <v>wang@example.com</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>王小明</v>
-      </c>
-      <c r="F3" t="str">
-        <v>國一</v>
-      </c>
-      <c r="G3" t="str">
-        <v>台北市立中正國中</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2012-03-15</v>
-      </c>
-      <c r="I3" t="str">
-        <v>男</v>
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>年級填寫值</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-      <c r="C1" t="str">
-        <v>性別填寫值</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>小一</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>男</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>小二</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>女</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>小三</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>不提供</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>小四</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>小五</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>小六</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>國一</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>國二</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>國三</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>高一</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>高二</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>高三</v>
+    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>